--- a/Vouchers Mini app Template.xlsx
+++ b/Vouchers Mini app Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vodafone-my.sharepoint.com/personal/nikhil_lakha_vodacom_co_za/Documents/Documents/Month end reports/Month End Excel Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{D184D59B-BD6D-4165-9C33-FA428740CF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71154D2C-203F-43DE-9AAD-D818A580DA4A}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="8_{D184D59B-BD6D-4165-9C33-FA428740CF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7359214C-32E6-420C-8159-C5C22A688843}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="7" xr2:uid="{D2700157-EEE7-4249-B100-62561599C597}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{D2700157-EEE7-4249-B100-62561599C597}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="486">
   <si>
     <t>Last month</t>
   </si>
@@ -1370,6 +1370,141 @@
   </si>
   <si>
     <t>connection lost, please try again: unexpected end of json input</t>
+  </si>
+  <si>
+    <t>CVM Push Notifications</t>
+  </si>
+  <si>
+    <t>VFS CVM SMS Campaigns</t>
+  </si>
+  <si>
+    <t>Vodamedia</t>
+  </si>
+  <si>
+    <t>Connect U : Banner</t>
+  </si>
+  <si>
+    <t>Daily Unlock | Summer</t>
+  </si>
+  <si>
+    <t>TikTok for Business</t>
+  </si>
+  <si>
+    <t>Partner Newsletter | Panarottis</t>
+  </si>
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>campaign_network</t>
+  </si>
+  <si>
+    <t>clicks</t>
+  </si>
+  <si>
+    <t>sessions_d0</t>
+  </si>
+  <si>
+    <t>installs</t>
+  </si>
+  <si>
+    <t>voucher advance buy now success_events</t>
+  </si>
+  <si>
+    <t>voucher advance success_events</t>
+  </si>
+  <si>
+    <t>vodapay club subscription_events</t>
+  </si>
+  <si>
+    <t>Vouchers New and Existing Users</t>
+  </si>
+  <si>
+    <t>CVM WhatsApp Campaigns</t>
+  </si>
+  <si>
+    <t>Subscribe to VodaPay Club and Get A R20 Coupon</t>
+  </si>
+  <si>
+    <t>Subscribe to VodaPay Club and Get A discount</t>
+  </si>
+  <si>
+    <t>Betway Bucks Vouchers Awareness</t>
+  </si>
+  <si>
+    <t>VodaPay Club Channel Testing</t>
+  </si>
+  <si>
+    <t>ZA_26_AO_FIN_PAY_X_P_VP_00_005-26-372_VodaPay Club - Channel Test - FY26 – Q4 - TikTok - Auction - Subscription</t>
+  </si>
+  <si>
+    <t>Vouchers Dynamic Pricing</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>ZA_27_AO_FIN_PAY_X_P_VP_00_016-27-372_VodaPay Club Subscription Test - FY27 - Q1 - Telco - Facebook - Auction – Conversion</t>
+  </si>
+  <si>
+    <t>Vouchers</t>
+  </si>
+  <si>
+    <t>Subscribe to VodaPay Club and Get A Discount</t>
+  </si>
+  <si>
+    <t>Vouchers receipt tracking | Intercape Official</t>
+  </si>
+  <si>
+    <t>ZA_26_AO_FIN_PAY_X_P_VP_00_005-26-372_VodaPay Club - Channel Test - FY26 – Q4 - TikTok - Auction - Purchases</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Nandos | AO</t>
+  </si>
+  <si>
+    <t>ZA_25_AO_FIN_PAY_X_P_VP_00_035-25-372_VodaPay - Always On - FY25 - H2 - Vouchers - Auction - App Installs</t>
+  </si>
+  <si>
+    <t>VP Vouchers |SweepSouth| 40%</t>
+  </si>
+  <si>
+    <t>Vouchers | BP AO| Summer</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Panarottis | AO</t>
+  </si>
+  <si>
+    <t>MVA Voucher Advance</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Poetry | VPC 15%</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Spur| AO</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Cape Union and Old Khaki</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Generic | Club</t>
+  </si>
+  <si>
+    <t>VP Vouchers |bp| 10%</t>
+  </si>
+  <si>
+    <t>VP Vouchers |Travelwings | AO</t>
+  </si>
+  <si>
+    <t>Voucher Advance</t>
+  </si>
+  <si>
+    <t>VP Vouchers | Steers | AO</t>
+  </si>
+  <si>
+    <t>Vouchers Buy Now</t>
+  </si>
+  <si>
+    <t>Vouchers receipt tracking | Netflorist</t>
   </si>
 </sst>
 </file>
@@ -1434,6 +1569,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13907,13 +14046,902 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA28EAC7-7C68-4D48-AAC1-1B92AB9344D1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>333</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3">
+        <v>1169</v>
+      </c>
+      <c r="D3">
+        <v>33</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>127</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C4">
+        <v>360</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C5">
+        <v>19594</v>
+      </c>
+      <c r="D5">
+        <v>137</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>27</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6">
+        <v>15005</v>
+      </c>
+      <c r="D6">
+        <v>101</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>442</v>
+      </c>
+      <c r="B7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8">
+        <v>13900</v>
+      </c>
+      <c r="D8">
+        <v>530</v>
+      </c>
+      <c r="E8">
+        <v>161</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B11" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>444</v>
+      </c>
+      <c r="B13" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13">
+        <v>313208</v>
+      </c>
+      <c r="D13">
+        <v>975</v>
+      </c>
+      <c r="E13">
+        <v>348</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B14" t="s">
+        <v>467</v>
+      </c>
+      <c r="C14">
+        <v>15548</v>
+      </c>
+      <c r="D14">
+        <v>615</v>
+      </c>
+      <c r="E14">
+        <v>185</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>446</v>
+      </c>
+      <c r="B16" t="s">
+        <v>469</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>443</v>
+      </c>
+      <c r="B17" t="s">
+        <v>470</v>
+      </c>
+      <c r="C17">
+        <v>8835</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>441</v>
+      </c>
+      <c r="B18" t="s">
+        <v>461</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>446</v>
+      </c>
+      <c r="B19" t="s">
+        <v>471</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>443</v>
+      </c>
+      <c r="B20" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20">
+        <v>9660</v>
+      </c>
+      <c r="D20">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>445</v>
+      </c>
+      <c r="B21" t="s">
+        <v>473</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>447</v>
+      </c>
+      <c r="B22" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>442</v>
+      </c>
+      <c r="B23" t="s">
+        <v>475</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>443</v>
+      </c>
+      <c r="B24" t="s">
+        <v>476</v>
+      </c>
+      <c r="C24">
+        <v>5987</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>443</v>
+      </c>
+      <c r="B25" t="s">
+        <v>477</v>
+      </c>
+      <c r="C25">
+        <v>10996</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>443</v>
+      </c>
+      <c r="B26" t="s">
+        <v>478</v>
+      </c>
+      <c r="C26">
+        <v>8497</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>443</v>
+      </c>
+      <c r="B27" t="s">
+        <v>479</v>
+      </c>
+      <c r="C27">
+        <v>29258</v>
+      </c>
+      <c r="D27">
+        <v>48</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" t="s">
+        <v>480</v>
+      </c>
+      <c r="C28">
+        <v>22415</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>443</v>
+      </c>
+      <c r="B29" t="s">
+        <v>481</v>
+      </c>
+      <c r="C29">
+        <v>7528</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>441</v>
+      </c>
+      <c r="B30" t="s">
+        <v>482</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>445</v>
+      </c>
+      <c r="B31" t="s">
+        <v>483</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" t="s">
+        <v>484</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>442</v>
+      </c>
+      <c r="B33" t="s">
+        <v>463</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" t="s">
+        <v>485</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
